--- a/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
+++ b/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
@@ -66,7 +66,7 @@
     <numFmt numFmtId="168" formatCode="$#,##0"/>
     <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -141,6 +141,11 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="15"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -269,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -345,13 +350,14 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="19" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="19" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="20" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="20" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -359,17 +365,17 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="19" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="19" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="20" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="20" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="20" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -380,12 +386,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="19" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="22" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="22" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="20" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="20" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="23" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="22" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1321,7 +1327,7 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Set cell = the margin cell; it must contain a formula</t>
+          <t>The Set cell must contain a formula, so use the margin cell</t>
         </is>
       </c>
       <c r="D10" s="26" t="n"/>
@@ -1343,7 +1349,7 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Data → What-If Analysis → Data Table; the visits run down a column</t>
+          <t>The visits run down a column, so use the Column input cell</t>
         </is>
       </c>
       <c r="D11" s="27" t="n"/>
@@ -1426,7 +1432,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>Open Scenario Manager on the Model and add three scenarios that change B8, B16, B17 and B36. Base plan: visits per day 200, Medicaid share 14.9%, Commercial share 37.6%, billing fee 4.0%; Downside: visits per day 190, Medicaid share 17.9%, Commercial share 34.6%, billing fee 5.0%; Upside: visits per day 206, Medicaid share 12.9%, Commercial share 39.6%, billing fee 3.5%. Create a Scenario Summary with result cells B59 and B60. What is operating income in the Downside scenario? Round to the nearest dollar.</t>
+          <t>Open Scenario Manager on the Model and add three scenarios that change B8, B16, B17 and B36. Base plan: visits per day 200, Medicaid share 14.9%, Commercial share 37.6%, billing fee 4.0%. Downside: visits per day 190, Medicaid share 17.9%, Commercial share 34.6%, billing fee 5.0%. Upside: visits per day 206, Medicaid share 12.9%, Commercial share 39.6%, billing fee 3.5%. Create a Scenario Summary with result cells B59 and B60. What is operating income in the Downside scenario? Round to the nearest dollar.</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -1565,12 +1571,19 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Blue = input (change these) · Black = formula (don't type over) · Yellow = you complete it. Named cells: ClinicDays, VisitsPerDay, MedicaidShare, CommercialShare, CommercialRate, BillingFeePct, VisitsPerMonth, AvgReimbursement, NetRevenue, TotalExpenses, OperatingIncome, OperatingMargin.</t>
+          <t>Blue = input (change these) · Black = formula (don't type over) · Yellow = you complete it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Named cells (Formulas → Name Manager): ClinicDays, VisitsPerDay, MedicaidShare, CommercialShare, CommercialRate, BillingFeePct, VisitsPerMonth, AvgReimbursement, NetRevenue, TotalExpenses, OperatingIncome, OperatingMargin.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
@@ -1578,7 +1591,7 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="F5" s="31" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>SENSITIVITY AREA  (Data Tables)</t>
         </is>
@@ -1590,42 +1603,42 @@
       <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Volume &amp; capacity</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>Source / note</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="34" t="inlineStr">
         <is>
           <t>One-variable Data Table · Column input cell: B8</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>Clinic days per month</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="36" t="n">
         <v>21</v>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>days</t>
         </is>
@@ -1635,32 +1648,32 @@
           <t>Weekdays the clinic is open, less holidays (plan)</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>Visits per day</t>
         </is>
       </c>
-      <c r="G7" s="32" t="inlineStr">
+      <c r="G7" s="33" t="inlineStr">
         <is>
           <t>Operating income</t>
         </is>
       </c>
-      <c r="H7" s="32" t="inlineStr">
+      <c r="H7" s="33" t="inlineStr">
         <is>
           <t>Operating margin</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Visits per day</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="38" t="n">
         <v>200</v>
       </c>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>visits</t>
         </is>
@@ -1670,9 +1683,9 @@
           <t>FY2026 plan</t>
         </is>
       </c>
-      <c r="F8" s="34" t="n"/>
-      <c r="G8" s="38" t="n"/>
-      <c r="H8" s="39" t="n"/>
+      <c r="F8" s="35" t="n"/>
+      <c r="G8" s="39" t="n"/>
+      <c r="H8" s="40" t="n"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
           <t>← type =B59 and =B60 here (task 6)</t>
@@ -1680,15 +1693,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Physician FTEs (MD/DO)</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="38" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
@@ -1698,22 +1711,22 @@
           <t>Current staffing</t>
         </is>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="41" t="n">
         <v>180</v>
       </c>
-      <c r="G9" s="41" t="n"/>
-      <c r="H9" s="42" t="n"/>
+      <c r="G9" s="42" t="n"/>
+      <c r="H9" s="43" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>APP FTEs (NP/PA)</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
@@ -1723,22 +1736,22 @@
           <t>Current staffing</t>
         </is>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="41" t="n">
         <v>185</v>
       </c>
-      <c r="G10" s="41" t="n"/>
-      <c r="H10" s="42" t="n"/>
+      <c r="G10" s="42" t="n"/>
+      <c r="H10" s="43" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>Visits per physician per day</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="C11" s="36" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>visits</t>
         </is>
@@ -1748,22 +1761,22 @@
           <t>Scheduling template</t>
         </is>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="41" t="n">
         <v>190</v>
       </c>
-      <c r="G11" s="41" t="n"/>
-      <c r="H11" s="42" t="n"/>
+      <c r="G11" s="42" t="n"/>
+      <c r="H11" s="43" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Visits per APP per day</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>visits</t>
         </is>
@@ -1773,49 +1786,49 @@
           <t>Scheduling template</t>
         </is>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="41" t="n">
         <v>195</v>
       </c>
-      <c r="G12" s="41" t="n"/>
-      <c r="H12" s="42" t="n"/>
+      <c r="G12" s="42" t="n"/>
+      <c r="H12" s="43" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>Payer mix &amp; reimbursement</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>Share of visits</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>$ per visit</t>
         </is>
       </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>Source / note</t>
         </is>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="41" t="n">
         <v>200</v>
       </c>
-      <c r="G13" s="41" t="n"/>
-      <c r="H13" s="42" t="n"/>
+      <c r="G13" s="42" t="n"/>
+      <c r="H13" s="43" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>Medicare</t>
         </is>
       </c>
-      <c r="B14" s="43" t="n">
+      <c r="B14" s="44" t="n">
         <v>0.251</v>
       </c>
-      <c r="C14" s="44" t="n">
+      <c r="C14" s="45" t="n">
         <v>87</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1823,22 +1836,22 @@
           <t>2025 D400 claims (Sources)</t>
         </is>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="41" t="n">
         <v>205</v>
       </c>
-      <c r="G14" s="41" t="n"/>
-      <c r="H14" s="42" t="n"/>
+      <c r="G14" s="42" t="n"/>
+      <c r="H14" s="43" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>Medicare Advantage</t>
         </is>
       </c>
-      <c r="B15" s="43" t="n">
+      <c r="B15" s="44" t="n">
         <v>0.166</v>
       </c>
-      <c r="C15" s="44" t="n">
+      <c r="C15" s="45" t="n">
         <v>88</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1846,22 +1859,22 @@
           <t>2025 D400 claims (Sources)</t>
         </is>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="41" t="n">
         <v>210</v>
       </c>
-      <c r="G15" s="41" t="n"/>
-      <c r="H15" s="42" t="n"/>
+      <c r="G15" s="42" t="n"/>
+      <c r="H15" s="43" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>Medicaid</t>
         </is>
       </c>
-      <c r="B16" s="43" t="n">
+      <c r="B16" s="44" t="n">
         <v>0.149</v>
       </c>
-      <c r="C16" s="44" t="n">
+      <c r="C16" s="45" t="n">
         <v>66</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1869,22 +1882,22 @@
           <t>2025 D400 claims (Sources)</t>
         </is>
       </c>
-      <c r="F16" s="40" t="n">
+      <c r="F16" s="41" t="n">
         <v>215</v>
       </c>
-      <c r="G16" s="41" t="n"/>
-      <c r="H16" s="42" t="n"/>
+      <c r="G16" s="42" t="n"/>
+      <c r="H16" s="43" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>Commercial (incl. Workers' Comp)</t>
         </is>
       </c>
-      <c r="B17" s="43" t="n">
+      <c r="B17" s="44" t="n">
         <v>0.376</v>
       </c>
-      <c r="C17" s="44" t="n">
+      <c r="C17" s="45" t="n">
         <v>142</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1892,22 +1905,22 @@
           <t>2025 D400 claims (Sources)</t>
         </is>
       </c>
-      <c r="F17" s="40" t="n">
+      <c r="F17" s="41" t="n">
         <v>220</v>
       </c>
-      <c r="G17" s="41" t="n"/>
-      <c r="H17" s="42" t="n"/>
+      <c r="G17" s="42" t="n"/>
+      <c r="H17" s="43" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>Self-Pay</t>
         </is>
       </c>
-      <c r="B18" s="43" t="n">
+      <c r="B18" s="44" t="n">
         <v>0.058</v>
       </c>
-      <c r="C18" s="44" t="n">
+      <c r="C18" s="45" t="n">
         <v>120</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1922,12 +1935,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>Payer mix total (check)</t>
         </is>
       </c>
-      <c r="B19" s="46">
+      <c r="B19" s="47">
         <f>SUM(B14:B18)</f>
         <v/>
       </c>
@@ -1937,42 +1950,42 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>Staffing &amp; pay</t>
         </is>
       </c>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C20" s="32" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>Source / note</t>
         </is>
       </c>
-      <c r="F20" s="33" t="inlineStr">
+      <c r="F20" s="34" t="inlineStr">
         <is>
           <t>Two-variable Data Table · Row input cell: C17 · Column input cell: B8</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>RN FTEs</t>
         </is>
       </c>
-      <c r="B21" s="37" t="n">
+      <c r="B21" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="36" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
@@ -1982,27 +1995,27 @@
           <t>Current staffing</t>
         </is>
       </c>
-      <c r="F21" s="33" t="inlineStr">
+      <c r="F21" s="34" t="inlineStr">
         <is>
           <t>↓ Visits per day</t>
         </is>
       </c>
-      <c r="G21" s="47" t="inlineStr">
+      <c r="G21" s="48" t="inlineStr">
         <is>
           <t>Commercial $ per visit →</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>LPN FTEs</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="36" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
@@ -2012,33 +2025,33 @@
           <t>Current staffing</t>
         </is>
       </c>
-      <c r="F22" s="38" t="n"/>
-      <c r="G22" s="48" t="n">
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="49" t="n">
         <v>130</v>
       </c>
-      <c r="H22" s="48" t="n">
+      <c r="H22" s="49" t="n">
         <v>140</v>
       </c>
-      <c r="I22" s="48" t="n">
+      <c r="I22" s="49" t="n">
         <v>150</v>
       </c>
-      <c r="J22" s="48" t="n">
+      <c r="J22" s="49" t="n">
         <v>160</v>
       </c>
-      <c r="K22" s="48" t="n">
+      <c r="K22" s="49" t="n">
         <v>170</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>CNA FTEs</t>
         </is>
       </c>
-      <c r="B23" s="37" t="n">
+      <c r="B23" s="38" t="n">
         <v>8</v>
       </c>
-      <c r="C23" s="36" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
@@ -2048,25 +2061,25 @@
           <t>Current staffing</t>
         </is>
       </c>
-      <c r="F23" s="40" t="n">
+      <c r="F23" s="41" t="n">
         <v>180</v>
       </c>
-      <c r="G23" s="41" t="n"/>
-      <c r="H23" s="41" t="n"/>
-      <c r="I23" s="41" t="n"/>
-      <c r="J23" s="41" t="n"/>
-      <c r="K23" s="41" t="n"/>
+      <c r="G23" s="42" t="n"/>
+      <c r="H23" s="42" t="n"/>
+      <c r="I23" s="42" t="n"/>
+      <c r="J23" s="42" t="n"/>
+      <c r="K23" s="42" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>Front desk &amp; admin FTEs</t>
         </is>
       </c>
-      <c r="B24" s="37" t="n">
+      <c r="B24" s="38" t="n">
         <v>8</v>
       </c>
-      <c r="C24" s="36" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
@@ -2076,25 +2089,25 @@
           <t>Current staffing</t>
         </is>
       </c>
-      <c r="F24" s="40" t="n">
+      <c r="F24" s="41" t="n">
         <v>185</v>
       </c>
-      <c r="G24" s="41" t="n"/>
-      <c r="H24" s="41" t="n"/>
-      <c r="I24" s="41" t="n"/>
-      <c r="J24" s="41" t="n"/>
-      <c r="K24" s="41" t="n"/>
+      <c r="G24" s="42" t="n"/>
+      <c r="H24" s="42" t="n"/>
+      <c r="I24" s="42" t="n"/>
+      <c r="J24" s="42" t="n"/>
+      <c r="K24" s="42" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>Paid hours per FTE per month</t>
         </is>
       </c>
-      <c r="B25" s="35" t="n">
+      <c r="B25" s="36" t="n">
         <v>168</v>
       </c>
-      <c r="C25" s="36" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>hours</t>
         </is>
@@ -2104,25 +2117,25 @@
           <t>8-hour day × 21 clinic days</t>
         </is>
       </c>
-      <c r="F25" s="40" t="n">
+      <c r="F25" s="41" t="n">
         <v>190</v>
       </c>
-      <c r="G25" s="41" t="n"/>
-      <c r="H25" s="41" t="n"/>
-      <c r="I25" s="41" t="n"/>
-      <c r="J25" s="41" t="n"/>
-      <c r="K25" s="41" t="n"/>
+      <c r="G25" s="42" t="n"/>
+      <c r="H25" s="42" t="n"/>
+      <c r="I25" s="42" t="n"/>
+      <c r="J25" s="42" t="n"/>
+      <c r="K25" s="42" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>Physician salary per FTE</t>
         </is>
       </c>
-      <c r="B26" s="49" t="n">
+      <c r="B26" s="50" t="n">
         <v>22000</v>
       </c>
-      <c r="C26" s="36" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
@@ -2132,25 +2145,25 @@
           <t>FY2026 compensation plan</t>
         </is>
       </c>
-      <c r="F26" s="40" t="n">
+      <c r="F26" s="41" t="n">
         <v>195</v>
       </c>
-      <c r="G26" s="41" t="n"/>
-      <c r="H26" s="41" t="n"/>
-      <c r="I26" s="41" t="n"/>
-      <c r="J26" s="41" t="n"/>
-      <c r="K26" s="41" t="n"/>
+      <c r="G26" s="42" t="n"/>
+      <c r="H26" s="42" t="n"/>
+      <c r="I26" s="42" t="n"/>
+      <c r="J26" s="42" t="n"/>
+      <c r="K26" s="42" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>APP salary per FTE</t>
         </is>
       </c>
-      <c r="B27" s="49" t="n">
+      <c r="B27" s="50" t="n">
         <v>10800</v>
       </c>
-      <c r="C27" s="36" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
@@ -2160,25 +2173,25 @@
           <t>FY2026 compensation plan</t>
         </is>
       </c>
-      <c r="F27" s="40" t="n">
+      <c r="F27" s="41" t="n">
         <v>200</v>
       </c>
-      <c r="G27" s="41" t="n"/>
-      <c r="H27" s="41" t="n"/>
-      <c r="I27" s="41" t="n"/>
-      <c r="J27" s="41" t="n"/>
-      <c r="K27" s="41" t="n"/>
+      <c r="G27" s="42" t="n"/>
+      <c r="H27" s="42" t="n"/>
+      <c r="I27" s="42" t="n"/>
+      <c r="J27" s="42" t="n"/>
+      <c r="K27" s="42" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>RN hourly rate</t>
         </is>
       </c>
-      <c r="B28" s="44" t="n">
+      <c r="B28" s="45" t="n">
         <v>42.73</v>
       </c>
-      <c r="C28" s="36" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>$/hour</t>
         </is>
@@ -2188,25 +2201,25 @@
           <t>Median of active RNs (Sources)</t>
         </is>
       </c>
-      <c r="F28" s="40" t="n">
+      <c r="F28" s="41" t="n">
         <v>205</v>
       </c>
-      <c r="G28" s="41" t="n"/>
-      <c r="H28" s="41" t="n"/>
-      <c r="I28" s="41" t="n"/>
-      <c r="J28" s="41" t="n"/>
-      <c r="K28" s="41" t="n"/>
+      <c r="G28" s="42" t="n"/>
+      <c r="H28" s="42" t="n"/>
+      <c r="I28" s="42" t="n"/>
+      <c r="J28" s="42" t="n"/>
+      <c r="K28" s="42" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="34" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>LPN hourly rate</t>
         </is>
       </c>
-      <c r="B29" s="44" t="n">
+      <c r="B29" s="45" t="n">
         <v>27.73</v>
       </c>
-      <c r="C29" s="36" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>$/hour</t>
         </is>
@@ -2216,25 +2229,25 @@
           <t>Median of active LPNs (Sources)</t>
         </is>
       </c>
-      <c r="F29" s="40" t="n">
+      <c r="F29" s="41" t="n">
         <v>210</v>
       </c>
-      <c r="G29" s="41" t="n"/>
-      <c r="H29" s="41" t="n"/>
-      <c r="I29" s="41" t="n"/>
-      <c r="J29" s="41" t="n"/>
-      <c r="K29" s="41" t="n"/>
+      <c r="G29" s="42" t="n"/>
+      <c r="H29" s="42" t="n"/>
+      <c r="I29" s="42" t="n"/>
+      <c r="J29" s="42" t="n"/>
+      <c r="K29" s="42" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>CNA hourly rate</t>
         </is>
       </c>
-      <c r="B30" s="44" t="n">
+      <c r="B30" s="45" t="n">
         <v>19.74</v>
       </c>
-      <c r="C30" s="36" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
         <is>
           <t>$/hour</t>
         </is>
@@ -2244,25 +2257,25 @@
           <t>Median of active CNAs (Sources)</t>
         </is>
       </c>
-      <c r="F30" s="40" t="n">
+      <c r="F30" s="41" t="n">
         <v>215</v>
       </c>
-      <c r="G30" s="41" t="n"/>
-      <c r="H30" s="41" t="n"/>
-      <c r="I30" s="41" t="n"/>
-      <c r="J30" s="41" t="n"/>
-      <c r="K30" s="41" t="n"/>
+      <c r="G30" s="42" t="n"/>
+      <c r="H30" s="42" t="n"/>
+      <c r="I30" s="42" t="n"/>
+      <c r="J30" s="42" t="n"/>
+      <c r="K30" s="42" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>Front desk hourly rate</t>
         </is>
       </c>
-      <c r="B31" s="44" t="n">
+      <c r="B31" s="45" t="n">
         <v>18.86</v>
       </c>
-      <c r="C31" s="36" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
         <is>
           <t>$/hour</t>
         </is>
@@ -2272,25 +2285,25 @@
           <t>Median of active unit secretaries (Sources)</t>
         </is>
       </c>
-      <c r="F31" s="40" t="n">
+      <c r="F31" s="41" t="n">
         <v>220</v>
       </c>
-      <c r="G31" s="41" t="n"/>
-      <c r="H31" s="41" t="n"/>
-      <c r="I31" s="41" t="n"/>
-      <c r="J31" s="41" t="n"/>
-      <c r="K31" s="41" t="n"/>
+      <c r="G31" s="42" t="n"/>
+      <c r="H31" s="42" t="n"/>
+      <c r="I31" s="42" t="n"/>
+      <c r="J31" s="42" t="n"/>
+      <c r="K31" s="42" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>Benefits load (% of wages)</t>
         </is>
       </c>
-      <c r="B32" s="43" t="n">
+      <c r="B32" s="44" t="n">
         <v>0.267</v>
       </c>
-      <c r="C32" s="36" t="n"/>
+      <c r="C32" s="37" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t>2025 D400 benefits ÷ wages (Sources)</t>
@@ -2303,37 +2316,37 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>Other costs</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C33" s="32" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>Source / note</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="34" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>Medical supplies per visit</t>
         </is>
       </c>
-      <c r="B34" s="44" t="n">
+      <c r="B34" s="45" t="n">
         <v>4.39</v>
       </c>
-      <c r="C34" s="36" t="inlineStr">
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>$/visit</t>
         </is>
@@ -2345,15 +2358,15 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>Vaccines &amp; injectables per visit</t>
         </is>
       </c>
-      <c r="B35" s="44" t="n">
+      <c r="B35" s="45" t="n">
         <v>1.27</v>
       </c>
-      <c r="C35" s="36" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>$/visit</t>
         </is>
@@ -2365,15 +2378,15 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="34" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>Billing &amp; collections fee</t>
         </is>
       </c>
-      <c r="B36" s="43" t="n">
+      <c r="B36" s="44" t="n">
         <v>0.04</v>
       </c>
-      <c r="C36" s="36" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>of revenue</t>
         </is>
@@ -2385,15 +2398,15 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="34" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>Facility &amp; equipment</t>
         </is>
       </c>
-      <c r="B37" s="49" t="n">
+      <c r="B37" s="50" t="n">
         <v>11500</v>
       </c>
-      <c r="C37" s="36" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
@@ -2405,15 +2418,15 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="34" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>IT, EHR &amp; purchased services</t>
         </is>
       </c>
-      <c r="B38" s="49" t="n">
+      <c r="B38" s="50" t="n">
         <v>24200</v>
       </c>
-      <c r="C38" s="36" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
@@ -2425,15 +2438,15 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="34" t="inlineStr">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>Other operating</t>
         </is>
       </c>
-      <c r="B39" s="49" t="n">
+      <c r="B39" s="50" t="n">
         <v>14000</v>
       </c>
-      <c r="C39" s="36" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
@@ -2445,7 +2458,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="inlineStr">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t>CALCULATIONS  (one formula per row · no typed-in numbers)</t>
         </is>
@@ -2455,247 +2468,247 @@
       <c r="D41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>Visits per month</t>
         </is>
       </c>
-      <c r="B42" s="50">
+      <c r="B42" s="51">
         <f>VisitsPerDay*ClinicDays</f>
         <v/>
       </c>
-      <c r="C42" s="36" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
         <is>
           <t>visits</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="34" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>Average reimbursement per visit</t>
         </is>
       </c>
-      <c r="B43" s="51">
+      <c r="B43" s="52">
         <f>SUMPRODUCT(B14:B18,C14:C18)</f>
         <v/>
       </c>
-      <c r="C43" s="36" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
         <is>
           <t>$/visit</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="34" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>Net patient revenue</t>
         </is>
       </c>
-      <c r="B44" s="52">
+      <c r="B44" s="53">
         <f>VisitsPerMonth*AvgReimbursement</f>
         <v/>
       </c>
-      <c r="C44" s="36" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="34" t="inlineStr">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>Physician &amp; APP wages</t>
         </is>
       </c>
-      <c r="B45" s="52">
+      <c r="B45" s="53">
         <f>B9*B26+B10*B27</f>
         <v/>
       </c>
-      <c r="C45" s="36" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="34" t="inlineStr">
+      <c r="A46" s="35" t="inlineStr">
         <is>
           <t>Clinical support wages (RN, LPN, CNA)</t>
         </is>
       </c>
-      <c r="B46" s="52">
+      <c r="B46" s="53">
         <f>(B21*B28+B22*B29+B23*B30)*B25</f>
         <v/>
       </c>
-      <c r="C46" s="36" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="34" t="inlineStr">
+      <c r="A47" s="35" t="inlineStr">
         <is>
           <t>Front desk &amp; admin wages</t>
         </is>
       </c>
-      <c r="B47" s="52">
+      <c r="B47" s="53">
         <f>B24*B31*B25</f>
         <v/>
       </c>
-      <c r="C47" s="36" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="53" t="inlineStr">
+      <c r="A48" s="54" t="inlineStr">
         <is>
           <t>Total wages</t>
         </is>
       </c>
-      <c r="B48" s="54">
+      <c r="B48" s="55">
         <f>SUM(B45:B47)</f>
         <v/>
       </c>
-      <c r="C48" s="36" t="inlineStr">
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="34" t="inlineStr">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>Benefits</t>
         </is>
       </c>
-      <c r="B49" s="52">
+      <c r="B49" s="53">
         <f>B48*B32</f>
         <v/>
       </c>
-      <c r="C49" s="36" t="inlineStr">
+      <c r="C49" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="34" t="inlineStr">
+      <c r="A50" s="35" t="inlineStr">
         <is>
           <t>Medical supplies</t>
         </is>
       </c>
-      <c r="B50" s="52">
+      <c r="B50" s="53">
         <f>VisitsPerMonth*B34</f>
         <v/>
       </c>
-      <c r="C50" s="36" t="inlineStr">
+      <c r="C50" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="34" t="inlineStr">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t>Vaccines &amp; injectables</t>
         </is>
       </c>
-      <c r="B51" s="52">
+      <c r="B51" s="53">
         <f>VisitsPerMonth*B35</f>
         <v/>
       </c>
-      <c r="C51" s="36" t="inlineStr">
+      <c r="C51" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="34" t="inlineStr">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>Billing &amp; collections fee</t>
         </is>
       </c>
-      <c r="B52" s="52">
+      <c r="B52" s="53">
         <f>NetRevenue*0.04</f>
         <v/>
       </c>
-      <c r="C52" s="36" t="inlineStr">
+      <c r="C52" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="34" t="inlineStr">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>Facility &amp; equipment</t>
         </is>
       </c>
-      <c r="B53" s="52">
+      <c r="B53" s="53">
         <f>B37</f>
         <v/>
       </c>
-      <c r="C53" s="36" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="34" t="inlineStr">
+      <c r="A54" s="35" t="inlineStr">
         <is>
           <t>IT, EHR &amp; purchased services</t>
         </is>
       </c>
-      <c r="B54" s="52">
+      <c r="B54" s="53">
         <f>B38</f>
         <v/>
       </c>
-      <c r="C54" s="36" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="34" t="inlineStr">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>Other operating</t>
         </is>
       </c>
-      <c r="B55" s="52">
+      <c r="B55" s="53">
         <f>B39</f>
         <v/>
       </c>
-      <c r="C55" s="36" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="53" t="inlineStr">
+      <c r="A56" s="54" t="inlineStr">
         <is>
           <t>Total operating expenses</t>
         </is>
       </c>
-      <c r="B56" s="55">
+      <c r="B56" s="56">
         <f>SUM(B48:B55)</f>
         <v/>
       </c>
-      <c r="C56" s="36" t="inlineStr">
+      <c r="C56" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31" t="inlineStr">
+      <c r="A58" s="32" t="inlineStr">
         <is>
           <t>OUTPUTS</t>
         </is>
@@ -2705,13 +2718,13 @@
       <c r="D58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="53" t="inlineStr">
+      <c r="A59" s="54" t="inlineStr">
         <is>
           <t>Operating income</t>
         </is>
       </c>
-      <c r="B59" s="38" t="n"/>
-      <c r="C59" s="36" t="inlineStr">
+      <c r="B59" s="39" t="n"/>
+      <c r="C59" s="37" t="inlineStr">
         <is>
           <t>$/month</t>
         </is>
@@ -2723,13 +2736,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="53" t="inlineStr">
+      <c r="A60" s="54" t="inlineStr">
         <is>
           <t>Operating margin</t>
         </is>
       </c>
-      <c r="B60" s="39" t="n"/>
-      <c r="C60" s="36" t="inlineStr">
+      <c r="B60" s="40" t="n"/>
+      <c r="C60" s="37" t="inlineStr">
         <is>
           <t>of revenue</t>
         </is>
@@ -2741,32 +2754,32 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="34" t="inlineStr">
+      <c r="A61" s="35" t="inlineStr">
         <is>
           <t>Cost per visit</t>
         </is>
       </c>
-      <c r="B61" s="51">
+      <c r="B61" s="52">
         <f>TotalExpenses/VisitsPerMonth</f>
         <v/>
       </c>
-      <c r="C61" s="36" t="inlineStr">
+      <c r="C61" s="37" t="inlineStr">
         <is>
           <t>$/visit</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="34" t="inlineStr">
+      <c r="A62" s="35" t="inlineStr">
         <is>
           <t>Visit capacity per day</t>
         </is>
       </c>
-      <c r="B62" s="34">
+      <c r="B62" s="35">
         <f>B9*B11+B10*B12</f>
         <v/>
       </c>
-      <c r="C62" s="36" t="inlineStr">
+      <c r="C62" s="37" t="inlineStr">
         <is>
           <t>visits</t>
         </is>
@@ -2778,16 +2791,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="34" t="inlineStr">
+      <c r="A63" s="35" t="inlineStr">
         <is>
           <t>Capacity utilization</t>
         </is>
       </c>
-      <c r="B63" s="56">
+      <c r="B63" s="57">
         <f>VisitsPerDay/B62</f>
         <v/>
       </c>
-      <c r="C63" s="36" t="inlineStr">
+      <c r="C63" s="37" t="inlineStr">
         <is>
           <t>of capacity</t>
         </is>
@@ -2821,7 +2834,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2840,7 +2853,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
@@ -2851,36 +2864,36 @@
       <c r="E5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Visits per day to staff for</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>visits</t>
         </is>
       </c>
-      <c r="D6" s="57" t="inlineStr">
+      <c r="D6" s="58" t="inlineStr">
         <is>
           <t>Model base case. The bonus changes it.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>Clinic days per month</t>
         </is>
       </c>
-      <c r="B7" s="58">
+      <c r="B7" s="59">
         <f>Model!B7</f>
         <v/>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>days</t>
         </is>
@@ -2892,108 +2905,108 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Visits per month</t>
         </is>
       </c>
-      <c r="B8" s="50">
+      <c r="B8" s="51">
         <f>B6*B7</f>
         <v/>
       </c>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>visits</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Support hours needed per visit (RN + LPN + CNA)</t>
         </is>
       </c>
-      <c r="B9" s="59" t="n">
+      <c r="B9" s="60" t="n">
         <v>0.6</v>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>hours</t>
         </is>
       </c>
-      <c r="D9" s="57" t="inlineStr">
+      <c r="D9" s="58" t="inlineStr">
         <is>
           <t>Rooming, vitals, injections, care coordination (time study)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>Licensed hours needed per visit (RN + LPN only)</t>
         </is>
       </c>
-      <c r="B10" s="59" t="n">
+      <c r="B10" s="60" t="n">
         <v>0.28</v>
       </c>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>hours</t>
         </is>
       </c>
-      <c r="D10" s="57" t="inlineStr">
+      <c r="D10" s="58" t="inlineStr">
         <is>
           <t>Triage calls, medications, patient teaching</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>Minimum RN share of licensed FTEs</t>
         </is>
       </c>
-      <c r="B11" s="60" t="n">
+      <c r="B11" s="61" t="n">
         <v>0.6</v>
       </c>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="57" t="inlineStr">
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="58" t="inlineStr">
         <is>
           <t>Clinic policy</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>CNA cap</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>FTEs</t>
         </is>
       </c>
-      <c r="D12" s="57" t="inlineStr">
+      <c r="D12" s="58" t="inlineStr">
         <is>
           <t>Approved CNA positions (bonus only)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>Paid hours per FTE per month</t>
         </is>
       </c>
-      <c r="B13" s="58">
+      <c r="B13" s="59">
         <f>Model!B25</f>
         <v/>
       </c>
-      <c r="C13" s="36" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>hours</t>
         </is>
@@ -3005,16 +3018,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>Benefits load</t>
         </is>
       </c>
-      <c r="B14" s="61">
+      <c r="B14" s="62">
         <f>Model!B32</f>
         <v/>
       </c>
-      <c r="C14" s="36" t="n"/>
+      <c r="C14" s="37" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>From the Model</t>
@@ -3022,7 +3035,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>DECISION VARIABLES  (Solver changes the green cells)</t>
         </is>
@@ -3033,117 +3046,117 @@
       <c r="E16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>FTEs</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>Hourly rate</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>Cost per FTE per month</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>Monthly cost</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>Registered Nurse (RN)</t>
         </is>
       </c>
-      <c r="B18" s="62" t="n">
+      <c r="B18" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="63">
+      <c r="C18" s="64">
         <f>Model!B28</f>
         <v/>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="52">
         <f>C18*$B$13*(1+$B$14)</f>
         <v/>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="53">
         <f>B18*D18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>Licensed Practical Nurse (LPN)</t>
         </is>
       </c>
-      <c r="B19" s="62" t="n">
+      <c r="B19" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="63">
+      <c r="C19" s="64">
         <f>Model!B29</f>
         <v/>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="52">
         <f>C19*$B$13*(1+$B$14)</f>
         <v/>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="53">
         <f>B19*D19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>Certified Nursing Assistant (CNA)</t>
         </is>
       </c>
-      <c r="B20" s="62" t="n">
+      <c r="B20" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="63">
+      <c r="C20" s="64">
         <f>Model!B30</f>
         <v/>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="52">
         <f>C20*$B$13*(1+$B$14)</f>
         <v/>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="53">
         <f>B20*D20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="64" t="inlineStr">
+      <c r="A21" s="65" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B21" s="65">
+      <c r="B21" s="66">
         <f>SUM(B18:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="64" t="n"/>
-      <c r="D21" s="64" t="n"/>
-      <c r="E21" s="55">
+      <c r="C21" s="65" t="n"/>
+      <c r="D21" s="65" t="n"/>
+      <c r="E21" s="56">
         <f>SUM(E18:E20)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>CONSTRAINTS  (each row: Provided  sign  Required)</t>
         </is>
@@ -3154,129 +3167,129 @@
       <c r="E23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>Constraint</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Provided</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>Sign</t>
         </is>
       </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E24" s="32" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>Total support hours</t>
         </is>
       </c>
-      <c r="B25" s="66">
+      <c r="B25" s="67">
         <f>B21*B13</f>
         <v/>
       </c>
-      <c r="C25" s="67" t="inlineStr">
+      <c r="C25" s="68" t="inlineStr">
         <is>
           <t>≥</t>
         </is>
       </c>
-      <c r="D25" s="66">
+      <c r="D25" s="67">
         <f>B8*B9</f>
         <v/>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="35">
         <f>IF(B25&gt;=D25-0.001,"OK","Short")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>Licensed hours (RN + LPN)</t>
         </is>
       </c>
-      <c r="B26" s="66">
+      <c r="B26" s="67">
         <f>(B18+B19)*B13</f>
         <v/>
       </c>
-      <c r="C26" s="67" t="inlineStr">
+      <c r="C26" s="68" t="inlineStr">
         <is>
           <t>≥</t>
         </is>
       </c>
-      <c r="D26" s="66">
+      <c r="D26" s="67">
         <f>B8*B10</f>
         <v/>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="35">
         <f>IF(B26&gt;=D26-0.001,"OK","Short")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>RN rule: RN FTEs − 60% × (RN + LPN FTEs)</t>
         </is>
       </c>
-      <c r="B27" s="68">
+      <c r="B27" s="69">
         <f>B18-B11*(B18+B19)</f>
         <v/>
       </c>
-      <c r="C27" s="67" t="inlineStr">
+      <c r="C27" s="68" t="inlineStr">
         <is>
           <t>≥</t>
         </is>
       </c>
-      <c r="D27" s="68" t="n">
+      <c r="D27" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="35">
         <f>IF(B27&gt;=D27-0.001,"OK","Short")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>CNA FTEs (bonus only)</t>
         </is>
       </c>
-      <c r="B28" s="68">
+      <c r="B28" s="69">
         <f>B20</f>
         <v/>
       </c>
-      <c r="C28" s="67" t="inlineStr">
+      <c r="C28" s="68" t="inlineStr">
         <is>
           <t>≤</t>
         </is>
       </c>
-      <c r="D28" s="68">
+      <c r="D28" s="69">
         <f>B12</f>
         <v/>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="35">
         <f>IF(B28&lt;=D28+0.001,"OK","Over cap (bonus only)")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>OBJECTIVE</t>
         </is>
@@ -3287,12 +3300,12 @@
       <c r="E30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="69" t="inlineStr">
+      <c r="A31" s="70" t="inlineStr">
         <is>
           <t>Monthly clinical support staff cost (minimize)</t>
         </is>
       </c>
-      <c r="B31" s="55">
+      <c r="B31" s="56">
         <f>E21</f>
         <v/>
       </c>
@@ -3307,7 +3320,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3320,27 +3333,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="69" t="inlineStr">
+      <c r="A1" s="70" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>Model cell</t>
         </is>
       </c>
-      <c r="C1" s="69" t="inlineStr">
+      <c r="C1" s="70" t="inlineStr">
         <is>
           <t>Value used</t>
         </is>
       </c>
-      <c r="D1" s="69" t="inlineStr">
+      <c r="D1" s="70" t="inlineStr">
         <is>
           <t>How it was derived</t>
         </is>
       </c>
-      <c r="E1" s="69" t="inlineStr">
+      <c r="E1" s="70" t="inlineStr">
         <is>
           <t>Source data</t>
         </is>
@@ -3915,6 +3928,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -4118,46 +4132,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="70" t="inlineStr">
+      <c r="A1" s="71" t="inlineStr">
         <is>
           <t>🔑 Answer Key — Lesson 3.6</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="72" t="inlineStr">
+      <c r="A4" s="73" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="72" t="inlineStr">
+      <c r="B4" s="73" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="72" t="inlineStr">
+      <c r="C4" s="73" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="72" t="inlineStr">
+      <c r="D4" s="73" t="inlineStr">
         <is>
           <t>Sample solution</t>
         </is>
       </c>
-      <c r="E4" s="72" t="inlineStr">
+      <c r="E4" s="73" t="inlineStr">
         <is>
           <t>Live result</t>
         </is>
       </c>
-      <c r="F4" s="72" t="inlineStr">
+      <c r="F4" s="73" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -4174,15 +4188,15 @@
           <t>On the Model sheet, complete the yellow Operating income cell (B59): net patient revenue minus total operating expenses. The gray cell here reads your formula. What is the clinic's base-case operating income per month?</t>
         </is>
       </c>
-      <c r="C5" s="73" t="n">
+      <c r="C5" s="74" t="n">
         <v>-8618.719999999999</v>
       </c>
-      <c r="D5" s="74" t="inlineStr">
+      <c r="D5" s="75" t="inlineStr">
         <is>
           <t>=B44-B56</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="75">
+      <c r="E5" cm="1" s="76">
         <f t="array" ref="E5">Model!B44-Model!B56</f>
         <v/>
       </c>
@@ -4203,15 +4217,15 @@
           <t>Complete the yellow Operating margin cell (B60): operating income as a share of net patient revenue. What is the base-case operating margin? (Format it as a percentage.)</t>
         </is>
       </c>
-      <c r="C6" s="76" t="n">
+      <c r="C6" s="77" t="n">
         <v>-0.01924463992647546</v>
       </c>
-      <c r="D6" s="74" t="inlineStr">
+      <c r="D6" s="75" t="inlineStr">
         <is>
           <t>=B59/B44</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="77">
+      <c r="E6" cm="1" s="78">
         <f t="array" ref="E6">(Model!B44-Model!B56)/Model!B44</f>
         <v/>
       </c>
@@ -4232,12 +4246,12 @@
           <t>Audit the model. One formula in the CALCULATIONS section (rows 42–56) has a number typed into it instead of a reference to its input cell. Type that cell's address (for example B99). Then fix the formula so it points to the input. Task 10 depends on the fix.</t>
         </is>
       </c>
-      <c r="C7" s="78" t="inlineStr">
+      <c r="C7" s="79" t="inlineStr">
         <is>
           <t>B52</t>
         </is>
       </c>
-      <c r="D7" s="74" t="inlineStr">
+      <c r="D7" s="75" t="inlineStr">
         <is>
           <t>1. Press **Ctrl + `** (Mac: **⌃ + `**) to show formulas, and read down rows 42–56.
 2. B52 reads `=NetRevenue*0.04`. The 4% is typed in, although the fee has its own input cell, B36.
@@ -4251,7 +4265,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>Today both versions return the same number, so nothing looks wrong. The trouble starts when someone changes the fee input in B36: the model ignores it. Another way to catch this is Formulas → Trace Dependents on B36. Excel finds no dependents and beeps (or says so in a message), because no formula reads that input.</t>
+          <t>Today both versions return the same number, so nothing looks wrong. The trouble starts when someone changes the fee input in B36: the model ignores it. Another way to catch this is Formulas → Trace Dependents on B36. Excel draws no arrows and tells you no formula refers to the active cell, because no formula reads that input.</t>
         </is>
       </c>
     </row>
@@ -4266,17 +4280,17 @@
           <t>Use Goal Seek to find the break-even volume: set Operating income to 0 by changing Visits per day (Model!B8). How many visits per day does the clinic need? Round to 1 decimal place, then click Cancel to restore 200.</t>
         </is>
       </c>
-      <c r="C8" s="79" t="n">
+      <c r="C8" s="80" t="n">
         <v>204.2</v>
       </c>
-      <c r="D8" s="74" t="inlineStr">
+      <c r="D8" s="75" t="inlineStr">
         <is>
           <t>1. Choose **Data → What-If Analysis → Goal Seek**.
 2. **Set cell:** `B59` · **To value:** `0` · **By changing cell:** `B8`.
 3. Click **OK**. B8 shows about 204.2440. Note it, then click **Cancel**.</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="80">
+      <c r="E8" cm="1" s="81">
         <f t="array" ref="E8">ROUND(Model!B8-(Model!B44-Model!B56)/((Model!B43*(1-Model!B36)-Model!B34-Model!B35)*Model!B7),1)</f>
         <v/>
       </c>
@@ -4297,17 +4311,17 @@
           <t>The CFO is renegotiating commercial contracts. Use Goal Seek to set Operating margin to 5% (type 0.05) by changing the Commercial $ per visit (Model!C17). What commercial reimbursement per visit is needed? Round to the nearest dollar, then click Cancel to restore $142.</t>
         </is>
       </c>
-      <c r="C9" s="81" t="n">
+      <c r="C9" s="82" t="n">
         <v>163.58</v>
       </c>
-      <c r="D9" s="74" t="inlineStr">
+      <c r="D9" s="75" t="inlineStr">
         <is>
           <t>1. **Data → What-If Analysis → Goal Seek**.
 2. **Set cell:** `B60` · **To value:** `0.05` · **By changing cell:** `C17`.
 3. Click **OK**, read C17, and click **Cancel**.</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="82">
+      <c r="E9" cm="1" s="83">
         <f t="array" ref="E9">Model!C17+((Model!B56-Model!B52)/(1-Model!B36-0.05)/Model!B42-Model!B43)/Model!B17</f>
         <v/>
       </c>
@@ -4328,10 +4342,10 @@
           <t>Build the one-variable Data Table in Model!F8:H17: put =B59 in G8 and =B60 in H8, select F8:H17, and use Column input cell B8. What operating margin does your table show at 190 visits per day? Enter it as a percentage to 1 decimal place.</t>
         </is>
       </c>
-      <c r="C10" s="76" t="n">
+      <c r="C10" s="77" t="n">
         <v>-0.06799013420112369</v>
       </c>
-      <c r="D10" s="74" t="inlineStr">
+      <c r="D10" s="75" t="inlineStr">
         <is>
           <t>=Model!H11</t>
         </is>
@@ -4358,10 +4372,10 @@
           <t>Look down the Operating income column of your one-variable table. What is the lowest visits-per-day value in the table at which the clinic makes a profit (operating income above 0)?</t>
         </is>
       </c>
-      <c r="C11" s="78" t="n">
+      <c r="C11" s="79" t="n">
         <v>205</v>
       </c>
-      <c r="D11" s="74" t="inlineStr">
+      <c r="D11" s="75" t="inlineStr">
         <is>
           <t>=MINIFS(Model!F9:F17,Model!G9:G17,"&gt;0")</t>
         </is>
@@ -4388,10 +4402,10 @@
           <t>Build the two-variable Data Table: put =B59 in the corner cell F22, select F22:K31, and use Row input cell C17 (commercial $ across row 22) and Column input cell B8 (visits per day down column F). What operating income does the table show at 210 visits per day and $160 per commercial visit? Round to the nearest dollar.</t>
         </is>
       </c>
-      <c r="C12" s="83" t="n">
+      <c r="C12" s="84" t="n">
         <v>40342</v>
       </c>
-      <c r="D12" s="74" t="inlineStr">
+      <c r="D12" s="75" t="inlineStr">
         <is>
           <t>=Model!J29</t>
         </is>
@@ -4407,7 +4421,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="96" customHeight="1">
+    <row r="13" ht="126" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -4418,10 +4432,10 @@
           <t>How many of the 45 combinations in your two-variable table (G23:K31) are profitable (operating income above 0)? Use a formula.</t>
         </is>
       </c>
-      <c r="C13" s="78" t="n">
+      <c r="C13" s="79" t="n">
         <v>24</v>
       </c>
-      <c r="D13" s="74" t="inlineStr">
+      <c r="D13" s="75" t="inlineStr">
         <is>
           <t>=COUNTIF(Model!G23:K31,"&gt;0")</t>
         </is>
@@ -4433,7 +4447,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>Ordinary formulas can read a Data Table's results, so you can summarize or chart them, or add conditional formatting. The profitable combinations sit in the bottom-right of the table, where volume and rate are both high. That pattern tells the CFO that a better contract and more visits each lower the volume the clinic needs to break even.</t>
+          <t>Ordinary formulas can read a Data Table's results, so you can count them, chart them, or add conditional formatting. The profitable combinations sit in the bottom-right of the table, where volume and rate are both high. Reading down each column shows the trade-off the CFO cares about: at $130 per commercial visit the clinic first makes money at 215 visits a day, but at $170 it does at 185. A better contract lowers the volume the clinic needs to break even.</t>
         </is>
       </c>
     </row>
@@ -4445,13 +4459,13 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>Open Scenario Manager on the Model and add three scenarios that change B8, B16, B17 and B36. Base plan: visits per day 200, Medicaid share 14.9%, Commercial share 37.6%, billing fee 4.0%; Downside: visits per day 190, Medicaid share 17.9%, Commercial share 34.6%, billing fee 5.0%; Upside: visits per day 206, Medicaid share 12.9%, Commercial share 39.6%, billing fee 3.5%. Create a Scenario Summary with result cells B59 and B60. What is operating income in the Downside scenario? Round to the nearest dollar.</t>
-        </is>
-      </c>
-      <c r="C14" s="83" t="n">
+          <t>Open Scenario Manager on the Model and add three scenarios that change B8, B16, B17 and B36. Base plan: visits per day 200, Medicaid share 14.9%, Commercial share 37.6%, billing fee 4.0%. Downside: visits per day 190, Medicaid share 17.9%, Commercial share 34.6%, billing fee 5.0%. Upside: visits per day 206, Medicaid share 12.9%, Commercial share 39.6%, billing fee 3.5%. Create a Scenario Summary with result cells B59 and B60. What is operating income in the Downside scenario? Round to the nearest dollar.</t>
+        </is>
+      </c>
+      <c r="C14" s="84" t="n">
         <v>-41824</v>
       </c>
-      <c r="D14" s="74" t="inlineStr">
+      <c r="D14" s="75" t="inlineStr">
         <is>
           <t>1. Select B8, then Ctrl-click (Mac: ⌘-click) B16:B17 and B36.
 2. **Data → What-If Analysis → Scenario Manager → Add…**. Name it *Base plan* and click **OK**. The values box shows the current values, so click **OK** again.
@@ -4481,10 +4495,10 @@
           <t>From the same Scenario Summary, what operating margin does the Upside scenario produce? Enter it as a percentage to 1 decimal place.</t>
         </is>
       </c>
-      <c r="C15" s="76" t="n">
+      <c r="C15" s="77" t="n">
         <v>0.02611461384491819</v>
       </c>
-      <c r="D15" s="74" t="inlineStr">
+      <c r="D15" s="75" t="inlineStr">
         <is>
           <t>Read the Upside column of the OperatingMargin row on the Scenario Summary sheet.</t>
         </is>
@@ -4511,10 +4525,10 @@
           <t>On the Staffing sheet, use Solver to minimize the monthly staff cost (B31) by changing the RN, LPN, and CNA FTEs (B18:B20), subject to the three constraints in rows 25–27 (leave out the CNA cap in row 28). Keep Make Unconstrained Variables Non-Negative ticked and choose Simplex LP. What is the minimum monthly cost? Round to the nearest dollar.</t>
         </is>
       </c>
-      <c r="C16" s="83" t="n">
+      <c r="C16" s="84" t="n">
         <v>88342</v>
       </c>
-      <c r="D16" s="74" t="inlineStr">
+      <c r="D16" s="75" t="inlineStr">
         <is>
           <t>=Staffing!B31</t>
         </is>
@@ -4530,7 +4544,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="126" customHeight="1">
+    <row r="17" ht="141" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
           <t>13</t>
@@ -4541,23 +4555,23 @@
           <t>Run Solver again (same setup) and select Sensitivity under Reports before you click OK. On the Sensitivity Report sheet, what is the Shadow Price of the Total support hours constraint (Staffing!B25)? Enter it in dollars to 2 decimal places.</t>
         </is>
       </c>
-      <c r="C17" s="81" t="n">
+      <c r="C17" s="82" t="n">
         <v>25.01</v>
       </c>
-      <c r="D17" s="74" t="inlineStr">
+      <c r="D17" s="75" t="inlineStr">
         <is>
           <t>1. **Data → Solver**, same parameters as task 12, **Solve**.
 2. In **Solver Results**, select **Sensitivity** under *Reports*, then click **OK**.
 3. On the new *Sensitivity Report 1* sheet, find the row for `$B$25` under *Constraints* and read **Shadow Price**.</t>
         </is>
       </c>
-      <c r="E17" cm="1" s="82">
+      <c r="E17" cm="1" s="83">
         <f t="array" ref="E17">ROUND(Model!B30*(1+Model!B32),2)</f>
         <v/>
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>Requiring one more support hour raises the minimum cost by $25.01. That's one CNA hour at $19.74 plus 26.7% benefits, because the cheapest way to cover an hour that doesn't need a licensed nurse is a CNA hour. The live result in the key repeats that arithmetic. The licensed-hours constraint has a higher shadow price ($21.53). An extra licensed hour costs 0.6 RN hours plus 0.4 LPN hours, but it also replaces a CNA hour that's no longer needed.</t>
+          <t>Requiring one more support hour raises the minimum cost by $25.01. That's one CNA hour at $19.74 plus 26.7% benefits, because the cheapest way to cover an hour that doesn't need a licensed nurse is a CNA hour. The live result in the key repeats that arithmetic. The licensed-hours constraint (B26) has a shadow price of only $21.53, even though licensed nurses cost more. An extra licensed hour costs 0.6 RN hours plus 0.4 LPN hours, but licensed hours also count toward the total, so it replaces a CNA hour that's no longer needed.</t>
         </is>
       </c>
     </row>
@@ -4589,46 +4603,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="70" t="inlineStr">
+      <c r="A1" s="71" t="inlineStr">
         <is>
           <t>🔑 Bonus Key — Lesson 3.6</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="72" t="inlineStr">
+      <c r="A4" s="73" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="72" t="inlineStr">
+      <c r="B4" s="73" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="72" t="inlineStr">
+      <c r="C4" s="73" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="72" t="inlineStr">
+      <c r="D4" s="73" t="inlineStr">
         <is>
           <t>Sample solution</t>
         </is>
       </c>
-      <c r="E4" s="72" t="inlineStr">
+      <c r="E4" s="73" t="inlineStr">
         <is>
           <t>Live result</t>
         </is>
       </c>
-      <c r="F4" s="72" t="inlineStr">
+      <c r="F4" s="73" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -4645,10 +4659,10 @@
           <t>On the Staffing sheet, change B6 to 220. Re-run Solver with two more constraints: B18:B20 = int (integer) and B28 &lt;= D28 (the CNA cap). In Solver Options, set Integer Optimality (%) to 0. What is the minimum monthly staff cost? Round to the nearest dollar.</t>
         </is>
       </c>
-      <c r="C5" s="83" t="n">
+      <c r="C5" s="84" t="n">
         <v>112488</v>
       </c>
-      <c r="D5" s="74" t="inlineStr">
+      <c r="D5" s="75" t="inlineStr">
         <is>
           <t>1. Type 220 in Staffing!B6.
 2. **Data → Solver**. Keep the objective, variable cells, and the three constraints from task 12.
@@ -4679,10 +4693,10 @@
           <t>How many RNs does that plan hire?</t>
         </is>
       </c>
-      <c r="C6" s="78" t="n">
+      <c r="C6" s="79" t="n">
         <v>7</v>
       </c>
-      <c r="D6" s="74" t="inlineStr">
+      <c r="D6" s="75" t="inlineStr">
         <is>
           <t>Read Staffing!B18 after Solver finishes.</t>
         </is>
@@ -4709,10 +4723,10 @@
           <t>How many LPNs does that plan hire?</t>
         </is>
       </c>
-      <c r="C7" s="78" t="n">
+      <c r="C7" s="79" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="74" t="inlineStr">
+      <c r="D7" s="75" t="inlineStr">
         <is>
           <t>Read Staffing!B19 after Solver finishes.</t>
         </is>
@@ -4739,12 +4753,12 @@
           <t>Test the plan in the P&amp;L. On the Model, add two more scenarios that change B8, B10 and B21:B23: Today (200, 3, 5, 3, 8) and Growth 2026 (220, 4, and your RN, LPN, and CNA counts). What operating income does Growth 2026 produce? Round to the nearest dollar.</t>
         </is>
       </c>
-      <c r="C8" s="83" t="n">
+      <c r="C8" s="84" t="n">
         <v>2624</v>
       </c>
-      <c r="D8" s="74" t="inlineStr">
-        <is>
-          <t>1. On the Model, select B8, B10 and B21:B23 (Ctrl-click; Mac: ⌘-click).
+      <c r="D8" s="75" t="inlineStr">
+        <is>
+          <t>1. On the Model, select B8, B10 and B21:B23 (Ctrl-click, or ⌘-click on a Mac).
 2. **Scenario Manager → Add…** *Today*: 200, 3, 5, 3, 8.
 3. **Add…** *Growth 2026*: 220, 4, 7, 4, 6.
 4. **Summary…** with result cells `B59,B60`, or select Growth 2026, click **Show**, read B59, then **Show** Today to restore the base case.</t>

--- a/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
+++ b/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
@@ -274,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -437,6 +437,9 @@
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -842,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C32"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -850,6 +853,7 @@
     <col width="95" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -871,6 +875,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -927,6 +932,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -1019,7 +1025,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="33" customHeight="1">
+    <row r="20" ht="48" customHeight="1">
       <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -1027,7 +1033,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Goal Seek, Scenario Manager, and Solver change input cells. Put the base case back after each run so the other tasks stay correct.</t>
+          <t>Goal Seek and Scenario Manager's Show button change the Model's input cells. Put the base case back after each run so the other tasks stay correct. Solver only changes the Staffing sheet, which doesn't feed the Model.</t>
         </is>
       </c>
     </row>
@@ -1043,6 +1049,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
         <is>
@@ -1099,6 +1106,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
@@ -1176,7 +1184,7 @@
     <row r="2" ht="49" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Every task uses the Model and Staffing sheets. Tasks 1 and 2 read your Model live, so their checks stay green only while the Model holds its base-case inputs (200 visits per day, Commercial $142, and so on). After each what-if run, put the original values back: click Cancel in the Goal Seek Status box, and choose Restore Original Values in the Solver Results box.</t>
+          <t>Every task uses the Model and Staffing sheets. Tasks 1 and 2 read your Model live, so their checks stay green only while the Model holds its base-case inputs (200 visits per day, Commercial $142, and so on). After each Goal Seek run, click Cancel in the Goal Seek Status box so the Model keeps those inputs. The Staffing sheet doesn't feed the Model, so you can keep Solver's solutions there.</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2122,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>8-hour day × 21 clinic days</t>
+          <t>Full-time paid hours per month (plan)</t>
         </is>
       </c>
       <c r="F25" s="41" t="n">
@@ -2457,6 +2465,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="32" t="inlineStr">
         <is>
@@ -2707,6 +2716,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
@@ -2852,6 +2862,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="32" t="inlineStr">
         <is>
@@ -3034,6 +3046,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="32" t="inlineStr">
         <is>
@@ -3155,6 +3168,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="32" t="inlineStr">
         <is>
@@ -3288,6 +3302,7 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="32" t="inlineStr">
         <is>
@@ -3512,7 +3527,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Average AllowedAmount per 2025 D400 claim = $86.83 (denied claims count as $0), rounded to the dollar</t>
+          <t>Average AllowedAmount per 2025 D400 claim = $86.83 (denied and appealed claims carry an AllowedAmount of $0 and count as $0), rounded to the dollar</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -3539,7 +3554,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Average AllowedAmount per 2025 D400 claim = $87.88 (denied claims count as $0), rounded to the dollar</t>
+          <t>Average AllowedAmount per 2025 D400 claim = $87.88 (denied and appealed claims carry an AllowedAmount of $0 and count as $0), rounded to the dollar</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -3566,7 +3581,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Average AllowedAmount per 2025 D400 claim = $66.09 (denied claims count as $0), rounded to the dollar</t>
+          <t>Average AllowedAmount per 2025 D400 claim = $66.09 (denied and appealed claims carry an AllowedAmount of $0 and count as $0), rounded to the dollar</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3593,7 +3608,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Average AllowedAmount per 2025 D400 claim = $141.57 (denied claims count as $0), rounded to the dollar</t>
+          <t>Average AllowedAmount per 2025 D400 claim = $141.57 (denied and appealed claims carry an AllowedAmount of $0 and count as $0), rounded to the dollar</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -3620,7 +3635,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Average AllowedAmount per 2025 D400 claim = $120.13 (denied claims count as $0), rounded to the dollar</t>
+          <t>Average AllowedAmount per 2025 D400 claim = $120.13 (denied and appealed claims carry an AllowedAmount of $0 and count as $0), rounded to the dollar</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -4145,6 +4160,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="73" t="inlineStr">
         <is>
@@ -4287,11 +4303,11 @@
         <is>
           <t>1. Choose **Data → What-If Analysis → Goal Seek**.
 2. **Set cell:** `B59` · **To value:** `0` · **By changing cell:** `B8`.
-3. Click **OK**. B8 shows about 204.2440. Note it, then click **Cancel**.</t>
+3. Click **OK**. B8 shows 204.2 (the cell holds 204.2440…). Note it, then click **Cancel**.</t>
         </is>
       </c>
       <c r="E8" cm="1" s="81">
-        <f t="array" ref="E8">ROUND(Model!B8-(Model!B44-Model!B56)/((Model!B43*(1-Model!B36)-Model!B34-Model!B35)*Model!B7),1)</f>
+        <f t="array" ref="E8">ROUND(Model!B8-(Model!B44-Model!B56)/((Model!B43*(1-Model!B52/Model!B44)-Model!B34-Model!B35)*Model!B7),1)</f>
         <v/>
       </c>
       <c r="F8" s="19" t="inlineStr">
@@ -4322,7 +4338,7 @@
         </is>
       </c>
       <c r="E9" cm="1" s="83">
-        <f t="array" ref="E9">Model!C17+((Model!B56-Model!B52)/(1-Model!B36-0.05)/Model!B42-Model!B43)/Model!B17</f>
+        <f t="array" ref="E9">Model!C17+((Model!B56-Model!B52)/(1-Model!B52/Model!B44-0.05)/Model!B42-Model!B43)/Model!B17</f>
         <v/>
       </c>
       <c r="F9" s="19" t="inlineStr">
@@ -4361,7 +4377,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="81" customHeight="1">
+    <row r="11" ht="96" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
           <t>7</t>
@@ -4387,11 +4403,11 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>The table jumps in steps of 5, so it brackets the break-even point instead of finding it: 200 visits loses money and 205 makes money, which agrees with Goal Seek's 204.2. Use a Data Table to see the whole curve, and Goal Seek to pin down the exact crossing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="126" customHeight="1">
+          <t>The table jumps in steps of 5, so it brackets the break-even point instead of finding it: 200 visits loses money and 205 makes money, which agrees with Goal Seek's 204.2. Use a Data Table to see the whole curve, and Goal Seek to pin down the exact crossing. MINIFS needs Excel 2019 or later. In older versions, read the value off the table and type it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="171" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
           <t>8</t>
@@ -4417,7 +4433,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>A two-variable table has exactly one formula, in its top-left corner. Excel substitutes each top-row value into the row input cell (C17) and each left-column value into the column input cell (B8), and fills every intersection. If you swap the two input cells, the table still fills without any warning, but with wrong numbers. So check one cell by hand: at 200 visits and $140 the result should be close to the base case (−$8,619), because the base case is 200 visits at $142.</t>
+          <t>A two-variable table has exactly one formula, in its top-left corner. Excel substitutes each top-row value into the row input cell (C17) and each left-column value into the column input cell (B8), and fills every intersection. If you swap the two input cells, the table still fills without any warning, but with wrong numbers. So check one cell by hand. The base case is 200 visits at $142 (−$8,619), so the cell at 200 visits and $140 should be about $3,032 lower: $2 less on each of the 37.6% of visits that are commercial, after the 4% fee. With swapped input cells that cell would show 140 visits a day at $200, a far bigger loss.</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4530,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="156" customHeight="1">
+    <row r="16" ht="186" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>12</t>
@@ -4530,17 +4546,20 @@
       </c>
       <c r="D16" s="75" t="inlineStr">
         <is>
-          <t>=Staffing!B31</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>1. Choose **Data → Solver**.
+2. **Set Objective:** `$B$31` · **To:** Min · **By Changing Variable Cells:** `$B$18:$B$20`.
+3. Click **Add** and enter `$B$25:$B$27` **&gt;=** `$D$25:$D$27`, then click **OK**.
+4. Leave **Make Unconstrained Variables Non-Negative** ticked, choose **Simplex LP**, and click **Solve**.
+5. Choose **Keep Solver Solution**, click **OK**, and type the value of B31, rounded to the dollar, in the answer cell.</t>
+        </is>
+      </c>
+      <c r="E16" cm="1" s="85">
+        <f t="array" ref="E16">Staffing!B8*Staffing!B10/Staffing!B13*(Staffing!B11*Staffing!D18+(1-Staffing!B11)*Staffing!D19)+Staffing!B8*(Staffing!B9-Staffing!B10)/Staffing!B13*Staffing!D20</f>
+        <v/>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>Solver parameters: Set Objective $B$31, To Min, By Changing Variable Cells $B$18:$B$20, Subject to the Constraints $B$25:$B$27 &gt;= $D$25:$D$27, Simplex LP. Then keep the solution and point at (or type) B31. Solver chooses 4.2 RN, 2.8 LPN and 8.0 CNA FTEs. This answer makes sense: CNAs are the cheapest staff, so they cover every hour that doesn't need a licensed nurse. The licensed hours are then split at exactly the 60% RN minimum, because LPNs cost less than RNs. Today's 5/3/8 staffing costs $96,798, so the plan saves about $8,457 a month.</t>
+          <t>Solver chooses 4.2 RN, 2.8 LPN and 8.0 CNA FTEs. This answer makes sense: CNAs are the cheapest staff, so they cover every hour that doesn't need a licensed nurse. The licensed hours are then split at exactly the 60% RN minimum, because LPNs cost less than RNs. Today's 5/3/8 staffing costs $96,798, so the plan saves about $8,457 a month. Type the number rather than pointing at B31, because the bonus runs Solver on the same sheet again. The key's live result rebuilds this optimum with algebra from the Staffing sheet's own cells.</t>
         </is>
       </c>
     </row>
@@ -4616,6 +4635,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="73" t="inlineStr">
         <is>

--- a/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
+++ b/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
@@ -4407,7 +4407,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="171" customHeight="1">
+    <row r="12" ht="186" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
           <t>8</t>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>A two-variable table has exactly one formula, in its top-left corner. Excel substitutes each top-row value into the row input cell (C17) and each left-column value into the column input cell (B8), and fills every intersection. If you swap the two input cells, the table still fills without any warning, but with wrong numbers. So check one cell by hand. The base case is 200 visits at $142 (−$8,619), so the cell at 200 visits and $140 should be about $3,032 lower: $2 less on each of the 37.6% of visits that are commercial, after the 4% fee. With swapped input cells that cell would show 140 visits a day at $200, a far bigger loss.</t>
+          <t>A two-variable table has exactly one formula, in its top-left corner. Excel substitutes each top-row value into the row input cell (C17) and each left-column value into the column input cell (B8), and fills every intersection. If you swap the two input cells, the table still fills without any warning, but with wrong numbers. So check one cell by hand. The base case is 200 visits at $142 (−$8,619), so the cell at 200 visits and $140 should be about $3,032 lower, because the clinic's 1,579 commercial visits a month each pay $2 less, minus the 4% fee on those dollars. With swapped input cells that cell would show 140 visits a day at $200, a far bigger loss.</t>
         </is>
       </c>
     </row>

--- a/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
+++ b/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Model is the clinic's monthly P&amp;L, laid out as INPUTS (blue numbers), CALCULATIONS (black formulas), and OUTPUTS. You complete two yellow output cells and build two Data Tables in the Sensitivity area (columns F–K).</t>
+          <t>Model is the clinic's monthly profit and loss (P&amp;L) model, laid out as INPUTS (blue numbers), CALCULATIONS (black formulas), and OUTPUTS. You complete two yellow output cells and build two Data Tables in the Sensitivity area (columns F–K).</t>
         </is>
       </c>
     </row>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="49" customHeight="1">
+    <row r="2" ht="64" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Every task uses the Model and Staffing sheets. Tasks 1 and 2 read your Model live, so their checks stay green only while the Model holds its base-case inputs (200 visits per day, Commercial $142, and so on). After each Goal Seek run, click Cancel in the Goal Seek Status box so the Model keeps those inputs. The Staffing sheet doesn't feed the Model, so you can keep Solver's solutions there.</t>
+          <t>Every task uses the Model and Staffing sheets. Tasks 1 and 2 read your Model live, so their checks stay green only while the Model holds its base-case inputs (200 visits per day, Commercial $142, and so on). The same is true of any answer you type as a link to a Model cell, such as =Model!H11. After each Goal Seek run, click Cancel in the Goal Seek Status box so the Model keeps those inputs. The Staffing sheet doesn't feed the Model, so you can keep Solver's solutions there.</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Complete the yellow Operating margin cell (B60): operating income as a share of net patient revenue. What is the base-case operating margin? (Format it as a percentage.)</t>
+          <t>Complete the yellow Operating margin cell (B60): operating income as a share of net patient revenue. What is the base-case operating margin? The cell is already formatted as a percentage.</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -1300,7 +1300,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="51" customHeight="1">
+    <row r="9" ht="66" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>4</t>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Use Goal Seek to find the break-even volume: set Operating income to 0 by changing Visits per day (Model!B8). How many visits per day does the clinic need? Round to 1 decimal place, then click Cancel to restore 200.</t>
+          <t>On the Model sheet, use Goal Seek to find the break-even volume: set Operating income (B59) to 0 by changing Visits per day (B8). How many visits per day does the clinic need? Round to 1 decimal place, then click Cancel to restore 200.</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>The CFO is renegotiating commercial contracts. Use Goal Seek to set Operating margin to 5% (type 0.05) by changing the Commercial $ per visit (Model!C17). What commercial reimbursement per visit is needed? Round to the nearest dollar, then click Cancel to restore $142.</t>
+          <t>The CFO is renegotiating commercial contracts. On the Model sheet, use Goal Seek to set Operating margin (B60) to 5% (type 0.05) by changing the Commercial $ per visit (C17). What commercial reimbursement per visit is needed? Round to the nearest dollar, then click Cancel to restore $142.</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="81" customHeight="1">
+    <row r="17" ht="96" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
           <t>12</t>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>On the Staffing sheet, use Solver to minimize the monthly staff cost (B31) by changing the RN, LPN, and CNA FTEs (B18:B20), subject to the three constraints in rows 25–27 (leave out the CNA cap in row 28). Keep Make Unconstrained Variables Non-Negative ticked and choose Simplex LP. What is the minimum monthly cost? Round to the nearest dollar.</t>
+          <t>On the Staffing sheet, use Solver to minimize the monthly staff cost (B31) by changing the RN, LPN, and CNA FTEs (B18:B20), subject to the three constraints in rows 25–27 (leave out the CNA cap in row 28). Keep Make Unconstrained Variables Non-Negative ticked and choose Simplex LP. What is the minimum monthly cost? Round to the nearest dollar, and type the number rather than a link to B31, because the bonus runs Solver on this sheet again.</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -3977,7 +3977,7 @@
     <row r="2" ht="49" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Bluestone wants the Primary Care Clinic to grow to 220 visits per day in 2026 by adding a fourth APP (capacity rises from 208 to 226 visits per day). HR hires whole people, so every role needs a whole number of 1.0-FTE staff. Only 6 CNA positions are approved (Staffing!B12). Find the cheapest staffing plan, then test the full plan in the P&amp;L.</t>
+          <t>Bluestone wants the Primary Care Clinic to grow to 220 visits per day in 2026 by adding a fourth advanced practice provider (APP: a nurse practitioner or physician assistant). Capacity rises from 208 to 226 visits per day. HR hires whole people, so every role needs a whole number of 1.0-FTE staff. Only 6 CNA positions are approved (Staffing!B12). Find the cheapest staffing plan, then test the full plan in the Model's P&amp;L.</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Add an int constraint on the three variable cells</t>
+          <t>In Add Constraint, pick int from the middle list. Integer Optimality is on the All Methods tab of Options</t>
         </is>
       </c>
       <c r="D6" s="29" t="n"/>
@@ -4043,7 +4043,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
           <t>B2</t>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Look at B18</t>
+          <t>Read Staffing!B18. The RN rule in row 27 should still say OK</t>
         </is>
       </c>
       <c r="D7" s="28" t="n"/>
@@ -4087,7 +4087,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="66" customHeight="1">
+    <row r="9" ht="96" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>B4</t>
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Test the plan in the P&amp;L. On the Model, add two more scenarios that change B8, B10 and B21:B23: Today (200, 3, 5, 3, 8) and Growth 2026 (220, 4, and your RN, LPN, and CNA counts). What operating income does Growth 2026 produce? Round to the nearest dollar.</t>
+          <t>Test the plan in the P&amp;L. On the Model, first select the Base plan scenario and click Show, so the payer mix and billing fee are back at their base values. Then add two more scenarios that change B8, B10, and B21:B23 (visits per day, APP FTEs, and RN, LPN, and CNA FTEs, in that order): Today (200, 3, 5, 3, 8) and Growth 2026 (220, 4, and the RN, LPN, and CNA counts in Staffing!B18:B20). What operating income does Growth 2026 produce? Round to the nearest dollar.</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Scenario Manager can switch five inputs at once, and switch them back</t>
+          <t>A scenario changes only its own cells. Every other input keeps the value it has when you click Show</t>
         </is>
       </c>
       <c r="D9" s="29" t="n"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Complete the yellow Operating margin cell (B60): operating income as a share of net patient revenue. What is the base-case operating margin? (Format it as a percentage.)</t>
+          <t>Complete the yellow Operating margin cell (B60): operating income as a share of net patient revenue. What is the base-case operating margin? The cell is already formatted as a percentage.</t>
         </is>
       </c>
       <c r="C6" s="77" t="n">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="126" customHeight="1">
+    <row r="7" ht="156" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
           <t>3</t>
@@ -4269,9 +4269,9 @@
       </c>
       <c r="D7" s="75" t="inlineStr">
         <is>
-          <t>1. Press **Ctrl + `** (Mac: **⌃ + `**) to show formulas, and read down rows 42–56.
+          <t>1. On the Model sheet, choose **Formulas → Show Formulas** (or press the Show Formulas shortcut from section 2), and read down rows 42–56.
 2. B52 reads `=NetRevenue*0.04`. The 4% is typed in, although the fee has its own input cell, B36.
-3. Change B52 to `=NetRevenue*BillingFeePct` (or `=B44*B36`), then press Ctrl + ` again to show values.</t>
+3. Change B52 to `=NetRevenue*BillingFeePct` (or `=B44*B36`), then turn **Show Formulas** off again to see values.</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Use Goal Seek to find the break-even volume: set Operating income to 0 by changing Visits per day (Model!B8). How many visits per day does the clinic need? Round to 1 decimal place, then click Cancel to restore 200.</t>
+          <t>On the Model sheet, use Goal Seek to find the break-even volume: set Operating income (B59) to 0 by changing Visits per day (B8). How many visits per day does the clinic need? Round to 1 decimal place, then click Cancel to restore 200.</t>
         </is>
       </c>
       <c r="C8" s="80" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="D8" s="75" t="inlineStr">
         <is>
-          <t>1. Choose **Data → What-If Analysis → Goal Seek**.
+          <t>1. On the Model sheet, choose **Data → What-If Analysis → Goal Seek**.
 2. **Set cell:** `B59` · **To value:** `0` · **By changing cell:** `B8`.
 3. Click **OK**. B8 shows 204.2 (the cell holds 204.2440…). Note it, then click **Cancel**.</t>
         </is>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>The CFO is renegotiating commercial contracts. Use Goal Seek to set Operating margin to 5% (type 0.05) by changing the Commercial $ per visit (Model!C17). What commercial reimbursement per visit is needed? Round to the nearest dollar, then click Cancel to restore $142.</t>
+          <t>The CFO is renegotiating commercial contracts. On the Model sheet, use Goal Seek to set Operating margin (B60) to 5% (type 0.05) by changing the Commercial $ per visit (C17). What commercial reimbursement per visit is needed? Round to the nearest dollar, then click Cancel to restore $142.</t>
         </is>
       </c>
       <c r="C9" s="82" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="D9" s="75" t="inlineStr">
         <is>
-          <t>1. **Data → What-If Analysis → Goal Seek**.
+          <t>1. On the Model sheet, choose **Data → What-If Analysis → Goal Seek**.
 2. **Set cell:** `B60` · **To value:** `0.05` · **By changing cell:** `C17`.
 3. Click **OK**, read C17, and click **Cancel**.</t>
         </is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="186" customHeight="1">
+    <row r="16" ht="201" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>12</t>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>On the Staffing sheet, use Solver to minimize the monthly staff cost (B31) by changing the RN, LPN, and CNA FTEs (B18:B20), subject to the three constraints in rows 25–27 (leave out the CNA cap in row 28). Keep Make Unconstrained Variables Non-Negative ticked and choose Simplex LP. What is the minimum monthly cost? Round to the nearest dollar.</t>
+          <t>On the Staffing sheet, use Solver to minimize the monthly staff cost (B31) by changing the RN, LPN, and CNA FTEs (B18:B20), subject to the three constraints in rows 25–27 (leave out the CNA cap in row 28). Keep Make Unconstrained Variables Non-Negative ticked and choose Simplex LP. What is the minimum monthly cost? Round to the nearest dollar, and type the number rather than a link to B31, because the bonus runs Solver on this sheet again.</t>
         </is>
       </c>
       <c r="C16" s="84" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="D16" s="75" t="inlineStr">
         <is>
-          <t>1. Choose **Data → Solver**.
+          <t>1. On the Staffing sheet, choose **Data → Solver**.
 2. **Set Objective:** `$B$31` · **To:** Min · **By Changing Variable Cells:** `$B$18:$B$20`.
 3. Click **Add** and enter `$B$25:$B$27` **&gt;=** `$D$25:$D$27`, then click **OK**.
 4. Leave **Make Unconstrained Variables Non-Negative** ticked, choose **Simplex LP**, and click **Solve**.
@@ -4559,7 +4559,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>Solver chooses 4.2 RN, 2.8 LPN and 8.0 CNA FTEs. This answer makes sense: CNAs are the cheapest staff, so they cover every hour that doesn't need a licensed nurse. The licensed hours are then split at exactly the 60% RN minimum, because LPNs cost less than RNs. Today's 5/3/8 staffing costs $96,798, so the plan saves about $8,457 a month. Type the number rather than pointing at B31, because the bonus runs Solver on the same sheet again. The key's live result rebuilds this optimum with algebra from the Staffing sheet's own cells.</t>
+          <t>Solver chooses 4.2 RN, 2.8 LPN and 8.0 CNA FTEs. This answer makes sense: CNAs are the cheapest staff, so they cover every hour that doesn't need a licensed nurse. The licensed hours are then split at exactly the 60% RN minimum, because LPNs cost less than RNs. Today's 5/3/8 staffing costs $96,798, so the plan saves about $8,457 a month. The key's live result rebuilds this optimum with algebra from the Staffing sheet's own cells.</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>With fractions allowed, the cheapest plan costs $107,302 (6.3 RN, 4.2 LPN, 6.0 CNA). Requiring whole people raises that to $112,488, so indivisibility costs $5,186 a month. Solver handles integer constraints by branch and bound, solving many LPs with tighter and tighter bounds. Its default Integer Optimality of 1% lets it stop at any plan within 1% of the best possible, so set it to 0 when the exact answer matters.</t>
+          <t>With fractions allowed, the cheapest plan costs $107,302 (6.3 RN, 4.2 LPN, 6.0 CNA). Requiring whole people raises that to $112,488, so hiring whole people costs $5,186 a month more. Solver handles integer constraints by branch and bound, solving many LPs with tighter and tighter bounds. Its default Integer Optimality of 1% lets it stop at any plan within 1% of the best possible, so set it to 0 when the exact answer matters.</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="141" customHeight="1">
+    <row r="8" ht="186" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>B4</t>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Test the plan in the P&amp;L. On the Model, add two more scenarios that change B8, B10 and B21:B23: Today (200, 3, 5, 3, 8) and Growth 2026 (220, 4, and your RN, LPN, and CNA counts). What operating income does Growth 2026 produce? Round to the nearest dollar.</t>
+          <t>Test the plan in the P&amp;L. On the Model, first select the Base plan scenario and click Show, so the payer mix and billing fee are back at their base values. Then add two more scenarios that change B8, B10, and B21:B23 (visits per day, APP FTEs, and RN, LPN, and CNA FTEs, in that order): Today (200, 3, 5, 3, 8) and Growth 2026 (220, 4, and the RN, LPN, and CNA counts in Staffing!B18:B20). What operating income does Growth 2026 produce? Round to the nearest dollar.</t>
         </is>
       </c>
       <c r="C8" s="84" t="n">
@@ -4778,10 +4778,11 @@
       </c>
       <c r="D8" s="75" t="inlineStr">
         <is>
-          <t>1. On the Model, select B8, B10 and B21:B23 (Ctrl-click, or ⌘-click on a Mac).
-2. **Scenario Manager → Add…** *Today*: 200, 3, 5, 3, 8.
-3. **Add…** *Growth 2026*: 220, 4, 7, 4, 6.
-4. **Summary…** with result cells `B59,B60`, or select Growth 2026, click **Show**, read B59, then **Show** Today to restore the base case.</t>
+          <t>1. On the Model, open **Scenario Manager**, select *Base plan*, and click **Show**. Close the dialog.
+2. Select B8, B10, and B21:B23 (Ctrl-click, or ⌘-click on a Mac).
+3. **Scenario Manager → Add…** *Today*: 200, 3, 5, 3, 8.
+4. **Add…** *Growth 2026*: 220, 4, 7, 4, 6.
+5. **Summary…** with result cells `B59,B60`, or select Growth 2026, click **Show**, read B59, then **Show** Today to restore the base case.</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -4791,7 +4792,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>The growth plan turns a −$8,619 monthly loss into $2,624 (0.5% margin). The new APP costs $10,800 plus benefits, and the larger staff costs $15,690 more a month than today's. The extra 420 visits a month each contribute $96.71, which covers both. Using scenarios instead of overwriting inputs means one click (Show Today) puts the base case back for every other task.</t>
+          <t>The growth plan turns a −$8,619 monthly loss into $2,624 (0.5% margin). The new APP costs $10,800 plus benefits, and the larger staff costs $15,690 more a month than today's. The extra 420 visits a month each contribute $96.71, which covers both. Growth 2026 changes only its five cells, so it inherits the payer mix and billing fee already on the Model. If Upside was the last scenario you showed, Growth 2026 would quietly use Upside's mix and fee, which is why you show Base plan first. Using scenarios instead of overwriting inputs also means one click (Show Today) puts the base case back for every other task.</t>
         </is>
       </c>
     </row>

--- a/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
+++ b/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
@@ -412,13 +412,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -427,19 +427,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -965,7 +965,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>3. Check yourself</t>
@@ -973,7 +973,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red).</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 21 rows — Excel Table 'tblSources'</t>
+          <t>Data: 21 rows, in the Excel Table 'tblSources'</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="64" customHeight="1">
+    <row r="2" ht="49" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Every task uses the Model and Staffing sheets. Tasks 1 and 2 read your Model live, so their checks stay green only while the Model holds its base-case inputs (200 visits per day, Commercial $142, and so on). The same is true of any answer you type as a link to a Model cell, such as =Model!H11. After each Goal Seek run, click Cancel in the Goal Seek Status box so the Model keeps those inputs. The Staffing sheet doesn't feed the Model, so you can keep Solver's solutions there.</t>
@@ -4142,7 +4142,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4156,7 +4156,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="72" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="156" customHeight="1">
+    <row r="7" ht="141" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
           <t>3</t>
@@ -4269,9 +4269,9 @@
       </c>
       <c r="D7" s="75" t="inlineStr">
         <is>
-          <t>1. On the Model sheet, choose **Formulas → Show Formulas** (or press the Show Formulas shortcut from section 2), and read down rows 42–56.
-2. B52 reads `=NetRevenue*0.04`. The 4% is typed in, although the fee has its own input cell, B36.
-3. Change B52 to `=NetRevenue*BillingFeePct` (or `=B44*B36`), then turn **Show Formulas** off again to see values.</t>
+          <t>1. On the Model sheet, choose Formulas → Show Formulas (or press the Show Formulas shortcut from section 2), and read down rows 42–56.
+2. B52 reads =NetRevenue*0.04. The 4% is typed in, although the fee has its own input cell, B36.
+3. Change B52 to =NetRevenue*BillingFeePct (or =B44*B36), then turn Show Formulas off again to see values.</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -4301,9 +4301,9 @@
       </c>
       <c r="D8" s="75" t="inlineStr">
         <is>
-          <t>1. On the Model sheet, choose **Data → What-If Analysis → Goal Seek**.
-2. **Set cell:** `B59` · **To value:** `0` · **By changing cell:** `B8`.
-3. Click **OK**. B8 shows 204.2 (the cell holds 204.2440…). Note it, then click **Cancel**.</t>
+          <t>1. On the Model sheet, choose Data → What-If Analysis → Goal Seek.
+2. Set cell: B59 · To value: 0 · By changing cell: B8.
+3. Click OK. B8 shows 204.2 (the cell holds 204.2440…). Note it, then click Cancel.</t>
         </is>
       </c>
       <c r="E8" cm="1" s="81">
@@ -4332,9 +4332,9 @@
       </c>
       <c r="D9" s="75" t="inlineStr">
         <is>
-          <t>1. On the Model sheet, choose **Data → What-If Analysis → Goal Seek**.
-2. **Set cell:** `B60` · **To value:** `0.05` · **By changing cell:** `C17`.
-3. Click **OK**, read C17, and click **Cancel**.</t>
+          <t>1. On the Model sheet, choose Data → What-If Analysis → Goal Seek.
+2. Set cell: B60 · To value: 0.05 · By changing cell: C17.
+3. Click OK, read C17, and click Cancel.</t>
         </is>
       </c>
       <c r="E9" cm="1" s="83">
@@ -4484,9 +4484,9 @@
       <c r="D14" s="75" t="inlineStr">
         <is>
           <t>1. Select B8, then Ctrl-click (Mac: ⌘-click) B16:B17 and B36.
-2. **Data → What-If Analysis → Scenario Manager → Add…**. Name it *Base plan* and click **OK**. The values box shows the current values, so click **OK** again.
-3. Click **Add…** again for *Downside* and *Upside*. Type the values in the order B8, B16, B17, B36 (decimals like 0.179 for 17.9%).
-4. Click **Summary…**, choose **Scenario summary**, set **Result cells** to `B59,B60`, and click **OK**. Read the Downside column on the new Scenario Summary sheet.</t>
+2. Data → What-If Analysis → Scenario Manager → Add…. Name it Base plan and click OK. The values box shows the current values, so click OK again.
+3. Click Add… again for Downside and Upside. Type the values in the order B8, B16, B17, B36 (decimals like 0.179 for 17.9%).
+4. Click Summary…, choose Scenario summary, set Result cells to B59,B60, and click OK. Read the Downside column on the new Scenario Summary sheet.</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
@@ -4530,7 +4530,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="201" customHeight="1">
+    <row r="16" ht="186" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>12</t>
@@ -4546,11 +4546,11 @@
       </c>
       <c r="D16" s="75" t="inlineStr">
         <is>
-          <t>1. On the Staffing sheet, choose **Data → Solver**.
-2. **Set Objective:** `$B$31` · **To:** Min · **By Changing Variable Cells:** `$B$18:$B$20`.
-3. Click **Add** and enter `$B$25:$B$27` **&gt;=** `$D$25:$D$27`, then click **OK**.
-4. Leave **Make Unconstrained Variables Non-Negative** ticked, choose **Simplex LP**, and click **Solve**.
-5. Choose **Keep Solver Solution**, click **OK**, and type the value of B31, rounded to the dollar, in the answer cell.</t>
+          <t>1. On the Staffing sheet, choose Data → Solver.
+2. Set Objective: $B$31 · To: Min · By Changing Variable Cells: $B$18:$B$20.
+3. Click Add and enter $B$25:$B$27 &gt;= $D$25:$D$27, then click OK.
+4. Leave Make Unconstrained Variables Non-Negative ticked, choose Simplex LP, and click Solve.
+5. Choose Keep Solver Solution, click OK, and type the value of B31, rounded to the dollar, in the answer cell.</t>
         </is>
       </c>
       <c r="E16" cm="1" s="85">
@@ -4579,9 +4579,9 @@
       </c>
       <c r="D17" s="75" t="inlineStr">
         <is>
-          <t>1. **Data → Solver**, same parameters as task 12, **Solve**.
-2. In **Solver Results**, select **Sensitivity** under *Reports*, then click **OK**.
-3. On the new *Sensitivity Report 1* sheet, find the row for `$B$25` under *Constraints* and read **Shadow Price**.</t>
+          <t>1. Data → Solver, same parameters as task 12, Solve.
+2. In Solver Results, select Sensitivity under Reports, then click OK.
+3. On the new Sensitivity Report 1 sheet, find the row for $B$25 under Constraints and read Shadow Price.</t>
         </is>
       </c>
       <c r="E17" cm="1" s="83">
@@ -4617,7 +4617,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4631,7 +4631,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="72" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against, and column D shows a sample solution (steps or code).</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="171" customHeight="1">
+    <row r="5" ht="156" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
           <t>B1</t>
@@ -4685,10 +4685,10 @@
       <c r="D5" s="75" t="inlineStr">
         <is>
           <t>1. Type 220 in Staffing!B6.
-2. **Data → Solver**. Keep the objective, variable cells, and the three constraints from task 12.
-3. **Add** `$B$18:$B$20` **int** and **Add** `$B$28 &lt;= $D$28`.
-4. **Options** → *All Methods* tab → **Integer Optimality (%)** = 0 → **OK**. Check that **Ignore Integer Constraints** is not ticked.
-5. **Solve**, keep the solution, and read B31.</t>
+2. Data → Solver. Keep the objective, variable cells, and the three constraints from task 12.
+3. Add $B$18:$B$20 int and Add $B$28 &lt;= $D$28.
+4. Options → All Methods tab → Integer Optimality (%) = 0 → OK. Check that Ignore Integer Constraints is not ticked.
+5. Solve, keep the solution, and read B31.</t>
         </is>
       </c>
       <c r="E5" s="18" t="inlineStr">
@@ -4762,7 +4762,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="186" customHeight="1">
+    <row r="8" ht="171" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>B4</t>
@@ -4778,11 +4778,11 @@
       </c>
       <c r="D8" s="75" t="inlineStr">
         <is>
-          <t>1. On the Model, open **Scenario Manager**, select *Base plan*, and click **Show**. Close the dialog.
+          <t>1. On the Model, open Scenario Manager, select Base plan, and click Show. Close the dialog.
 2. Select B8, B10, and B21:B23 (Ctrl-click, or ⌘-click on a Mac).
-3. **Scenario Manager → Add…** *Today*: 200, 3, 5, 3, 8.
-4. **Add…** *Growth 2026*: 220, 4, 7, 4, 6.
-5. **Summary…** with result cells `B59,B60`, or select Growth 2026, click **Show**, read B59, then **Show** Today to restore the base case.</t>
+3. Scenario Manager → Add… Today: 200, 3, 5, 3, 8.
+4. Add… Growth 2026: 220, 4, 7, 4, 6.
+5. Summary… with result cells B59,B60, or select Growth 2026, click Show, read B59, then Show Today to restore the base case.</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">

--- a/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
+++ b/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -871,7 +871,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Intermediate  ·  about 60 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Intermediate  ·  about 125 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -1118,34 +1118,58 @@
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>13 practice tasks, each with a Check cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Data: 21 rows, in the Excel Table 'tblSources'</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="63" customHeight="1">
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>A monthly operating model for Bluestone's Primary Care Clinic (D400, Bluestone Outpatient Pavilion). Payer mix and reimbursement come from the clinic's 2,079 claims with 2025 service dates, wage rates from Bluestone HR records, and benefits, supply, and fixed costs from the clinic's 2025 budget actuals.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (4 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="63" customHeight="1">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>A monthly operating model for Bluestone's Primary Care Clinic (D400, Bluestone Outpatient Pavilion). Payer mix and reimbursement come from the clinic's 2,079 claims with 2025 service dates, wage rates from Bluestone HR records, and benefits, supply, and fixed costs from the clinic's 2025 budget actuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>

--- a/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
+++ b/03-data-analysis/06-what-if-analysis/3.6-what-if-analysis.xlsx
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -953,7 +953,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell.</t>
+          <t>Go to the 'Practice' sheet. For tasks 1 and 2, complete the yellow output cells on the Model sheet, and the task's gray cell on Practice reads them. For tasks 3–13, do the work on the Model or Staffing sheet, then type the answer into the task's yellow cell on Practice.</t>
         </is>
       </c>
     </row>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Model is the clinic's monthly profit and loss (P&amp;L) model, laid out as INPUTS (blue numbers), CALCULATIONS (black formulas), and OUTPUTS. You complete two yellow output cells and build two Data Tables in the Sensitivity area (columns F–K).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="33" customHeight="1">
+          <t>On the Model sheet, blue numbers are inputs and black cells are formulas. You complete two yellow output cells and build two Data Tables in the Sensitivity area (columns F–K). The Sources sheet shows where each data-derived input came from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
       <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -1021,11 +1021,11 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Staffing is a Solver worksheet. The green cells are the decision variables that Solver changes. Sources lists where every data-derived input came from.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1">
+          <t>Goal Seek and Scenario Manager's Show button change the Model's input cells. Put the base case back after each run so the other tasks stay correct. Solver only changes the Staffing sheet, which doesn't feed the Model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="33" customHeight="1">
       <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -1033,143 +1033,155 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Goal Seek and Scenario Manager's Show button change the Model's input cells. Put the base case back after each run so the other tasks stay correct. Solver only changes the Staffing sheet, which doesn't feed the Model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="33" customHeight="1">
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
           <t>Solver is a free add-in that ships with Excel. Turn it on once: File → Options → Add-ins → Manage: Excel Add-ins → Go → tick Solver Add-in (Mac: Tools → Excel Add-ins).</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Color legend</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Yellow cell</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Your answer goes here.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Yellow cell</t>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Gray cell</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Your answer goes here.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Gray cell</t>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>✔ Correct</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
+          <t>Your answer matches the key.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>✔ Correct</t>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>✘ Not yet</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Your answer matches the key.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>✘ Not yet</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
           <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Sheets in this workbook</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
+      <c r="C28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>13 practice tasks, each with a Check cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="33" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Practice</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>13 practice tasks, each with a Check cell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
+          <t>The clinic's monthly profit and loss (P&amp;L) model: inputs, calculations, outputs, and the Sensitivity area for your Data Tables (tasks 1–11 and bonus B4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="33" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Staffing</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 21 rows, in the Excel Table 'tblSources'</t>
+          <t>The Solver worksheet for the RN, LPN, and CNA staffing mix. The green cells are the decision variables (tasks 12–13 and bonus B1–B3).</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Data: 21 rows, in the Excel Table 'tblSources'</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
           <t>Bonus</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>The bonus challenge (4 parts).</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="63" customHeight="1">
-      <c r="B33" s="8" t="inlineStr">
+    <row r="34" ht="63" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>About the data</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>A monthly operating model for Bluestone's Primary Care Clinic (D400, Bluestone Outpatient Pavilion). Payer mix and reimbursement come from the clinic's 2,079 claims with 2025 service dates, wage rates from Bluestone HR records, and benefits, supply, and fixed costs from the clinic's 2025 budget actuals.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="8" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
@@ -4507,7 +4519,7 @@
       </c>
       <c r="D14" s="75" t="inlineStr">
         <is>
-          <t>1. Select B8, then Ctrl-click (Mac: ⌘-click) B16:B17 and B36.
+          <t>1. Select B8, then Ctrl + click (Mac: ⌘ + click) B16:B17 and B36.
 2. Data → What-If Analysis → Scenario Manager → Add…. Name it Base plan and click OK. The values box shows the current values, so click OK again.
 3. Click Add… again for Downside and Upside. Type the values in the order B8, B16, B17, B36 (decimals like 0.179 for 17.9%).
 4. Click Summary…, choose Scenario summary, set Result cells to B59,B60, and click OK. Read the Downside column on the new Scenario Summary sheet.</t>
@@ -4803,7 +4815,7 @@
       <c r="D8" s="75" t="inlineStr">
         <is>
           <t>1. On the Model, open Scenario Manager, select Base plan, and click Show. Close the dialog.
-2. Select B8, B10, and B21:B23 (Ctrl-click, or ⌘-click on a Mac).
+2. Select B8, B10, and B21:B23 (Ctrl + click, or ⌘ + click on a Mac).
 3. Scenario Manager → Add… Today: 200, 3, 5, 3, 8.
 4. Add… Growth 2026: 220, 4, 7, 4, 6.
 5. Summary… with result cells B59,B60, or select Growth 2026, click Show, read B59, then Show Today to restore the base case.</t>
